--- a/TestData/PMTest.xlsx
+++ b/TestData/PMTest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SynccIT\OneDrive\Desktop\2023-09 Eclipse\SMPL\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE5D167E-F1CC-44B5-B7A7-1026E01C0357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3CF9E6F-972D-4505-81CE-D7790021BEF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F4D0E5CD-1BC9-4424-9F39-51FA9D298B89}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="14">
   <si>
     <t>Section Name</t>
   </si>
@@ -42,132 +42,40 @@
     <t>Question</t>
   </si>
   <si>
-    <t>MECHANICAL-Ride</t>
-  </si>
-  <si>
-    <t>Check and ensure the condition of weld joints...</t>
-  </si>
-  <si>
-    <t>Keep and clean the whole hydraulic unit...</t>
-  </si>
-  <si>
-    <t>Check and ensure  the clamping and the tightening of the bolts
-for the coupling flanges between the base flanges module 0 or module 1. Bolt M30- torque 2200 Nm</t>
-  </si>
-  <si>
-    <t>Check  and ensure the clamping and the tightening of the bolts for the coupling flanges between the connecting flanges of  all the modules. Flangings are composed of: First Module Bolt M27- Torque 1650 Nm other Modules  Bolt M24- 1100 Nm</t>
-  </si>
-  <si>
-    <t>Check and ensure the clamping and the tightening of the bolts for the coupling between the pneumatic cylinders flanges and the support plate. Bolt M16- Torque 206 Nm</t>
-  </si>
-  <si>
-    <t>Check and ensure the structural integrity of all the carpentry parts of which the benches for passengers are made up of gondola.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check and ensure the structural integrity of each locking  lapbar paying particular attention to the weldings of supports, forks, boxes,etc .
-</t>
-  </si>
-  <si>
-    <t>Check and ensure the correct fixing of the supporting locks of the main closings on each gondola taking particular care of the welding.</t>
-  </si>
-  <si>
-    <t>Check and ensure the perfect functioning and the integrity of connecting pins between the safety lock transmission group and the safety bars. All pins should be equipped with split pin. Always keep the pins well lubricate by grease.</t>
-  </si>
-  <si>
-    <t>Check the perfect functioning and the integrity of
-connecting pins between the clamping hooks and the safety lock devices. All pins should be equipped with split pin. Always keep the pins well lubricate by grease.</t>
-  </si>
-  <si>
-    <t>Check the clamping and the tightening of the bolts for the coupling of the supporting locks. Flangings are composed of: Bolt M12- Torque 84 Nm</t>
-  </si>
-  <si>
-    <t>Check the clamping of the pins for the coupling between the locking lock and safety bar pipe. Flangings are composed of: Bolt M8- torque 25 Nm.</t>
-  </si>
-  <si>
-    <t>Check and ensure the correct fixing of the gas springs  and working of the bolts of the each gas springs.</t>
-  </si>
-  <si>
-    <t>Check and ensure the clamping of the bolts for the coupling between the safety belt and the passenger seat, and between the safety belt and the safety bar</t>
-  </si>
-  <si>
-    <t>Check and ensure the locking of the autobraking ring nuts for the pins of the pulley and check the presence of the security dowel. Check the presence of the rotation locks for the pins.</t>
-  </si>
-  <si>
-    <t>Check and ensure the locking of the ring nuts between the pulley support fork and the cylinder rod, check the presence of the security dowel.</t>
-  </si>
-  <si>
-    <t>Check and ensure the locking of the autobraking ring nuts for the pins of the pulley forks and check the presence of the security dowel. Check the presence of the rotation locks for the pins.</t>
-  </si>
-  <si>
-    <t>Check the clamping and the tightening of the bolts for the coupling flanges between the connecting flanges of pulleys forks slide on the pneumatic cylinders rods. Flangings are composed of: Bolt M20- torque 402 Nm</t>
-  </si>
-  <si>
-    <t>Check and ensure the clamping and the tightening of the bolts for the coupling between the brake cylinder  flanges and the support plate. Flangings are composed of: Bolt M16- torque 206 Nm.</t>
-  </si>
-  <si>
-    <t>Check and ensure the state of wear and the efficiency of the hydraulic buffers on module 1 and module 4 ( total 6 nos)</t>
-  </si>
-  <si>
-    <t>Check the clamping and the tightening of the bolts for the coupling between the hydraulic buffer flanges and the support plate on module 4. Flangings are composed of: Bolt M16- Torque 206 Nm</t>
-  </si>
-  <si>
-    <t>Check the clamping and the tightening of the bolts for the coupling between the hydraulic buffer support plate flanges and the module 4. Flangings are composed of: BOLT M20- torque 402 Nm.</t>
-  </si>
-  <si>
-    <t>Check the clamping and the tightening of the bolts for the coupling between the hydraulic buffer rod flanges and the support plate on module 4. Flangings are composed of: Bolt M16- Torque 206 Nm.</t>
-  </si>
-  <si>
-    <t>Check the clamping and the tightening of the bolts for the coupling between the hydraulic buffer flanges and the support plateorcolumn on module 0or1. Flangings are composed of: Bolt M16- Torque 206 Nm</t>
-  </si>
-  <si>
-    <t>Check the clamping and the tightening of the bolts for the coupling between the hydraulic buffer flanges and the support plate on module 1. Flangings are composed of: Bolt M16- Torque 206 Nm</t>
-  </si>
-  <si>
-    <t>Check the clamping and the tightening of the bolts for the coupling between the support plate of the hydraulic buffer flanges and the support flange on module 1. Flangings are composed of: Bolt m16- torque 206 Nm.</t>
-  </si>
-  <si>
-    <t>Check the state of wear and the general state of the bumpers of the boosters cylinders</t>
-  </si>
-  <si>
-    <t>Check the clamping and the tightening of the bolts for the coupling between the booster support plate flanges and the module 1. Flangings are composed of: Bolt M10- Torque 49 Nm.</t>
-  </si>
-  <si>
-    <t>check the clamping of the bolts for the coupling in the inspection platforms, the staircases and the protection railings (fences).
-Check also the structural integrity of all these parts.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lubricate the pin of each pulleyorpulleys group very well. </t>
-  </si>
-  <si>
-    <t>Lubricate the space between each pulleyorpulleys group very well.
-This operation must be carried out once a month, using of the silicone lubricant.</t>
-  </si>
-  <si>
-    <t>Check and Clean pneumatic cylinder rods and lubricate the same with oil.</t>
-  </si>
-  <si>
-    <t>Check the whole pneumatic system making sure of the integrity of all the pipes and of the absence of leakages both in the circuit and in the fillets.</t>
-  </si>
-  <si>
-    <t>Check the tension of the all wire ropes, in case of loose tight the wire rope as per the given procedure.</t>
-  </si>
-  <si>
-    <t>Check and ensure the freeness of guide wheels of gondola.</t>
-  </si>
-  <si>
-    <t>ELECTRICAL-Panel Room</t>
-  </si>
-  <si>
-    <t>ELECTRICAL-Compressor Room</t>
-  </si>
-  <si>
-    <t>ELECTRICAL-Hydraulic Motor</t>
-  </si>
-  <si>
-    <t>Check the maximum pressure</t>
-  </si>
-  <si>
-    <t>Check and ensure the proper tightness</t>
+    <t>Hardware Condition</t>
+  </si>
+  <si>
+    <t>Is the PC casing free from dust and damage?</t>
+  </si>
+  <si>
+    <t>Are all cables and connectors securely plugged in?</t>
+  </si>
+  <si>
+    <t>Is the cooling system (fans/liquid cooling) working properly?</t>
+  </si>
+  <si>
+    <t>Are peripherals (keyboard, mouse, headset) functioning correctly?</t>
+  </si>
+  <si>
+    <t>Is the monitor free from cracks and displaying correctly?</t>
+  </si>
+  <si>
+    <t>Software &amp; Network</t>
+  </si>
+  <si>
+    <t>Is the operating system up to date and running smoothly?</t>
+  </si>
+  <si>
+    <t>Are all required gaming applications installed and updated?</t>
+  </si>
+  <si>
+    <t>Is antivirus software active and virus definitions updated?</t>
+  </si>
+  <si>
+    <t>Is the PC connected to a stable and fast network?</t>
+  </si>
+  <si>
+    <t>Are user accounts and access permissions properly configured?</t>
   </si>
 </sst>
 </file>
@@ -522,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3D92625-8C69-408E-A500-3874FED55BA8}">
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.5546875" bestFit="1" customWidth="1"/>
@@ -541,297 +449,87 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>42</v>
+      <c r="B2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
+      <c r="B3" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>41</v>
+      <c r="B4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>2</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="72" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="72" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="72" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="72" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="72" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="72" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="72" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="72" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="72" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="72" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="72" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="72" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="72" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>37</v>
-      </c>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B12"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
